--- a/data/trans_orig/IQ11_1-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ11_1-Provincia-trans_orig.xlsx
@@ -1104,7 +1104,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3876</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,84%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4275</t>
+          <t>4304</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8257</t>
+          <t>8270</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2567</t>
+          <t>2486</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2562</t>
+          <t>3117</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>27,89%</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3024</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8613</t>
+          <t>8058</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2598</t>
+          <t>3483</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3598</t>
+          <t>3098</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>22,73%</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2804</t>
+          <t>3128</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3585</t>
+          <t>4052</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>29,73%</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>3933</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3910</t>
+          <t>3361</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8898</t>
+          <t>9081</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13103</t>
+          <t>13098</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3276,12 +3276,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,1%</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2572</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2413</t>
+          <t>2915</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>63,75%</t>
         </is>
       </c>
     </row>
@@ -4353,7 +4353,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2505</t>
+          <t>2501</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>40,47%</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>638</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3396</t>
+          <t>2721</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>4157</t>
+          <t>3585</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>650</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>5425</t>
+          <t>5438</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,7%</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>4125</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -5222,7 +5222,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>60,25%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>6149</t>
+          <t>6721</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -5257,7 +5257,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5277,12 +5277,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>11728</t>
+          <t>11715</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>16502</t>
+          <t>16503</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3298</t>
+          <t>3294</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>3315</t>
+          <t>3366</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>4117</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>4182</t>
+          <t>4133</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -6445,7 +6445,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>3815</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>7596</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>8649</t>
+          <t>9035</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>29249</t>
+          <t>29383</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>34419</t>
+          <t>34497</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>41252</t>
+          <t>41314</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6601,12 +6601,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>65767</t>
+          <t>65520</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>73660</t>
+          <t>73812</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6636,12 +6636,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,81%</t>
         </is>
       </c>
     </row>
@@ -7055,7 +7055,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2793</t>
+          <t>2877</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7070,7 +7070,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7105,7 +7105,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>53,02%</t>
         </is>
       </c>
     </row>
@@ -7388,7 +7388,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2784</t>
+          <t>2749</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2646</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,01%</t>
         </is>
       </c>
     </row>
@@ -7494,7 +7494,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7529,7 +7529,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2123</t>
+          <t>2231</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -7544,7 +7544,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>2978</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7707,7 +7707,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3712</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>15,0%</t>
         </is>
       </c>
     </row>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3349</t>
+          <t>3488</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7964,7 +7964,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>3205</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>17,95%</t>
         </is>
       </c>
     </row>
@@ -8025,7 +8025,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3417</t>
+          <t>2772</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3436</t>
+          <t>3434</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8110,7 +8110,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,24%</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4942</t>
+          <t>5059</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5539</t>
+          <t>5400</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -8181,7 +8181,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8201,12 +8201,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12781</t>
+          <t>13153</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17236</t>
+          <t>17230</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8216,12 +8216,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,52%</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2992</t>
+          <t>3441</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8379,7 +8379,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3420</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>16,33%</t>
         </is>
       </c>
     </row>
@@ -8475,7 +8475,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2970</t>
+          <t>2980</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8490,7 +8490,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3400</t>
+          <t>3573</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8525,7 +8525,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8545,7 +8545,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4238</t>
+          <t>4326</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8560,7 +8560,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,8%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>688</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5056</t>
+          <t>5110</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>648</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4950</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1487</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8029</t>
+          <t>7918</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,41%</t>
         </is>
       </c>
     </row>
@@ -8692,12 +8692,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>669</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5014</t>
+          <t>4877</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8707,12 +8707,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8732,7 +8732,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4280</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8747,7 +8747,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8762,12 +8762,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6983</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>31,85%</t>
         </is>
       </c>
     </row>
@@ -8803,12 +8803,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>1954</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7050</t>
+          <t>7023</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8818,12 +8818,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8838,12 +8838,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5429</t>
+          <t>6051</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11061</t>
+          <t>11010</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8916</t>
+          <t>9428</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16656</t>
+          <t>16679</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>72,48%</t>
         </is>
       </c>
     </row>
@@ -9293,7 +9293,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3366</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3926</t>
+          <t>3864</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9343,7 +9343,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>64,09%</t>
         </is>
       </c>
     </row>
@@ -9439,7 +9439,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9454,7 +9454,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>49,57%</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -9525,7 +9525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9545,7 +9545,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1817</t>
+          <t>1629</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -9560,7 +9560,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2708</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>66,93%</t>
         </is>
       </c>
     </row>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
@@ -10232,7 +10232,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -10602,7 +10602,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3625</t>
+          <t>3206</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10617,7 +10617,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10637,7 +10637,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3255</t>
+          <t>3606</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10652,7 +10652,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10667,12 +10667,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>449</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5584</t>
+          <t>5353</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10682,12 +10682,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>32,31%</t>
         </is>
       </c>
     </row>
@@ -10713,7 +10713,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4499</t>
+          <t>4986</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10728,7 +10728,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10748,7 +10748,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4173</t>
+          <t>4536</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10763,7 +10763,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10778,12 +10778,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1499</t>
+          <t>1515</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>7343</t>
+          <t>7180</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10793,12 +10793,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>43,33%</t>
         </is>
       </c>
     </row>
@@ -10819,12 +10819,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>5583</t>
+          <t>5588</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -10854,12 +10854,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>4690</t>
+          <t>4693</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>9425</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -10889,12 +10889,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>7281</t>
+          <t>7294</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>13731</t>
+          <t>13656</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -10904,12 +10904,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,42%</t>
         </is>
       </c>
     </row>
@@ -11163,7 +11163,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>3569</t>
+          <t>3701</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11178,7 +11178,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11233,7 +11233,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>3603</t>
+          <t>3637</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11248,7 +11248,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -11274,7 +11274,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2774</t>
+          <t>3382</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11289,7 +11289,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11304,12 +11304,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>629</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>4711</t>
+          <t>4697</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11319,12 +11319,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11339,12 +11339,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>649</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>6060</t>
+          <t>6099</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11354,12 +11354,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,71%</t>
         </is>
       </c>
     </row>
@@ -11385,7 +11385,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>4143</t>
+          <t>4027</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11415,12 +11415,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>615</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>4606</t>
+          <t>4669</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -11435,7 +11435,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -11450,12 +11450,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1323</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>6802</t>
+          <t>6837</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,22%</t>
         </is>
       </c>
     </row>
@@ -11491,12 +11491,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>6211</t>
+          <t>6292</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>11244</t>
+          <t>11267</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -11506,12 +11506,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11526,12 +11526,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>10229</t>
+          <t>10283</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>15671</t>
+          <t>16184</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -11541,12 +11541,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11561,12 +11561,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>18799</t>
+          <t>17955</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>26099</t>
+          <t>25586</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11576,12 +11576,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>86,89%</t>
         </is>
       </c>
     </row>
@@ -11961,7 +11961,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -11981,7 +11981,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>2692</t>
+          <t>2659</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -11996,7 +11996,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12016,7 +12016,7 @@
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>3687</t>
+          <t>3815</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12031,7 +12031,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>42,06%</t>
         </is>
       </c>
     </row>
@@ -12178,7 +12178,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>1383</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -12213,7 +12213,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -12233,7 +12233,7 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>5384</t>
+          <t>5256</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -12396,7 +12396,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>4988</t>
+          <t>4633</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12411,7 +12411,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>3243</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12446,7 +12446,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12461,12 +12461,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>626</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>5187</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12476,12 +12476,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -12507,7 +12507,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>5047</t>
+          <t>4397</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12522,7 +12522,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12542,7 +12542,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>2994</t>
+          <t>3377</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12557,7 +12557,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12577,7 +12577,7 @@
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>5686</t>
+          <t>5715</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12592,7 +12592,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -12613,12 +12613,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>8605</t>
+          <t>8624</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12628,12 +12628,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12648,12 +12648,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>3947</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>12652</t>
+          <t>12857</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12663,12 +12663,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12683,12 +12683,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>7103</t>
+          <t>7389</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>18118</t>
+          <t>17870</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12698,12 +12698,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,0%</t>
         </is>
       </c>
     </row>
@@ -12724,12 +12724,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>4055</t>
+          <t>4230</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>12869</t>
+          <t>12831</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12739,12 +12739,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12759,12 +12759,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>2560</t>
+          <t>2629</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>9943</t>
+          <t>10308</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12774,12 +12774,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12794,12 +12794,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>8084</t>
+          <t>8359</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>19594</t>
+          <t>19948</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,86%</t>
         </is>
       </c>
     </row>
@@ -12835,12 +12835,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>26454</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>36743</t>
+          <t>36979</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -12850,12 +12850,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -12870,12 +12870,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>44176</t>
+          <t>44629</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>55216</t>
+          <t>55352</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -12885,12 +12885,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>74886</t>
+          <t>74844</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>89764</t>
+          <t>89354</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>79,99%</t>
         </is>
       </c>
     </row>
@@ -13485,7 +13485,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2960</t>
+          <t>2999</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13500,7 +13500,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>35,1%</t>
         </is>
       </c>
     </row>
@@ -13672,7 +13672,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>4087</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -13687,7 +13687,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -13707,7 +13707,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4350</t>
+          <t>4560</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -13722,7 +13722,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>53,36%</t>
         </is>
       </c>
     </row>
@@ -13778,7 +13778,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2253</t>
+          <t>2078</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -13793,7 +13793,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -13813,12 +13813,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3777</t>
+          <t>3484</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7951</t>
+          <t>7991</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -13828,12 +13828,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,52%</t>
         </is>
       </c>
     </row>
@@ -14122,7 +14122,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2811</t>
+          <t>2851</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14137,7 +14137,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14157,7 +14157,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2813</t>
+          <t>3514</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14172,7 +14172,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>28,91%</t>
         </is>
       </c>
     </row>
@@ -14309,7 +14309,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3192</t>
+          <t>2540</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14324,7 +14324,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14344,7 +14344,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3273</t>
+          <t>3288</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14359,7 +14359,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14379,7 +14379,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3787</t>
+          <t>3827</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14394,7 +14394,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,49%</t>
         </is>
       </c>
     </row>
@@ -14415,7 +14415,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2161</t>
+          <t>2813</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -14430,7 +14430,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -14450,7 +14450,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3398</t>
+          <t>2724</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -14465,7 +14465,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -14485,12 +14485,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7533</t>
+          <t>7500</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11557</t>
+          <t>11565</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14500,12 +14500,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,14%</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2850</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -15703,7 +15703,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -15723,7 +15723,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3354</t>
+          <t>2914</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -15738,7 +15738,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>22,8%</t>
         </is>
       </c>
     </row>
@@ -15794,7 +15794,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4984</t>
+          <t>4963</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -15809,7 +15809,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -15829,7 +15829,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>9426</t>
+          <t>9866</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -15844,7 +15844,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -17628,7 +17628,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3683</t>
+          <t>3554</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -17643,7 +17643,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>54,02%</t>
         </is>
       </c>
     </row>
@@ -17704,7 +17704,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>2569</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -17719,7 +17719,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -17739,7 +17739,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3130</t>
+          <t>2520</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -17754,7 +17754,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>38,3%</t>
         </is>
       </c>
     </row>
@@ -17810,12 +17810,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>562</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3304</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -17825,12 +17825,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -17845,12 +17845,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2433</t>
+          <t>2513</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>5990</t>
+          <t>5978</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -17860,12 +17860,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>90,88%</t>
         </is>
       </c>
     </row>
@@ -18791,7 +18791,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -18806,7 +18806,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -18826,7 +18826,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>3088</t>
+          <t>3476</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -18841,7 +18841,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -18861,7 +18861,7 @@
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>4038</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -18876,7 +18876,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -18937,7 +18937,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>4335</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -18952,7 +18952,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -18972,7 +18972,7 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -18987,7 +18987,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -19013,7 +19013,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>2515</t>
+          <t>3153</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -19028,7 +19028,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -19043,12 +19043,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>7471</t>
+          <t>7517</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -19058,12 +19058,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>1754</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>8703</t>
+          <t>7831</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -19093,12 +19093,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>12,32%</t>
         </is>
       </c>
     </row>
@@ -19119,7 +19119,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>19503</t>
+          <t>19704</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -19134,7 +19134,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -19154,12 +19154,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>29881</t>
+          <t>30199</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>37481</t>
+          <t>37549</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -19169,12 +19169,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -19189,12 +19189,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>51471</t>
+          <t>51947</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>59823</t>
+          <t>59855</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -19204,12 +19204,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,19%</t>
         </is>
       </c>
     </row>
@@ -19880,7 +19880,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3731</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -19895,7 +19895,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>57,17%</t>
         </is>
       </c>
     </row>
@@ -20097,7 +20097,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3268</t>
+          <t>2999</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -20112,7 +20112,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -20628,7 +20628,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4112</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -20643,7 +20643,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -20663,7 +20663,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3802</t>
+          <t>3819</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -20678,7 +20678,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>47,62%</t>
         </is>
       </c>
     </row>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -20749,7 +20749,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -20769,7 +20769,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4218</t>
+          <t>4201</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -20784,7 +20784,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -23281,7 +23281,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2461</t>
+          <t>2553</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -23296,7 +23296,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -23351,7 +23351,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>3170</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -23366,7 +23366,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>54,81%</t>
         </is>
       </c>
     </row>
@@ -23387,7 +23387,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>881</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -23402,7 +23402,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -23457,7 +23457,7 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2281</t>
+          <t>2613</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
@@ -23472,7 +23472,7 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -23988,7 +23988,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>2707</t>
+          <t>2817</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -24003,7 +24003,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -24023,7 +24023,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3004</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -24038,7 +24038,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>30,26%</t>
         </is>
       </c>
     </row>
@@ -24094,7 +24094,7 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>4130</t>
+          <t>4020</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -24109,7 +24109,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -24129,7 +24129,7 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>7836</t>
+          <t>7560</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
@@ -24144,7 +24144,7 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -25256,7 +25256,7 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>2896</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -25271,7 +25271,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -25297,7 +25297,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>4887</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -25312,7 +25312,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -25327,12 +25327,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>627</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>7836</t>
+          <t>8607</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -25342,12 +25342,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -25362,12 +25362,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>9603</t>
+          <t>9605</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -25377,7 +25377,7 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -25403,7 +25403,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>12461</t>
+          <t>12895</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -25418,7 +25418,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -25438,12 +25438,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>16198</t>
+          <t>15427</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>23403</t>
+          <t>23407</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -25453,12 +25453,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -25473,12 +25473,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>30628</t>
+          <t>30400</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>39586</t>
+          <t>39565</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -25488,12 +25488,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>
